--- a/demo/聊城经开区“高标准农田建设专项整改排查”项目功能清单.xlsx
+++ b/demo/聊城经开区“高标准农田建设专项整改排查”项目功能清单.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="64">
   <si>
     <t>聊城经开区“高标准农田建设专项整改排查”项目功能清单</t>
   </si>
@@ -131,64 +131,64 @@
     <t>FD-09</t>
   </si>
   <si>
-    <t>数据字典</t>
+    <t>操作日志</t>
   </si>
   <si>
     <t>FD-10</t>
   </si>
   <si>
-    <t>操作日志</t>
+    <t>小程序</t>
+  </si>
+  <si>
+    <t>实现账号密码+验证码登录，登录后根据所属权限加载相应数据</t>
   </si>
   <si>
     <t>FD-11</t>
   </si>
   <si>
-    <t>小程序</t>
-  </si>
-  <si>
-    <t>实现账号密码+验证码登录，登录后根据所属权限加载相应数据</t>
+    <t>待办</t>
+  </si>
+  <si>
+    <t>列表</t>
+  </si>
+  <si>
+    <t>展示当前账号待整改的待办列表，支持点击定位查看地理位置</t>
   </si>
   <si>
     <t>FD-12</t>
   </si>
   <si>
-    <t>待办</t>
-  </si>
-  <si>
-    <t>列表</t>
-  </si>
-  <si>
-    <t>展示当前账号待整改的待办列表，支持点击定位查看地理位置</t>
+    <t>详情</t>
+  </si>
+  <si>
+    <t>查看待整改详细信息，填报整改反馈后闭环处置</t>
   </si>
   <si>
     <t>FD-13</t>
   </si>
   <si>
-    <t>详情</t>
-  </si>
-  <si>
-    <t>查看待整改详细信息，填报整改反馈后闭环处置</t>
+    <t>上报</t>
+  </si>
+  <si>
+    <t>获取权限</t>
+  </si>
+  <si>
+    <t>头像权限、定位权限、相机权限，未授权不可使用</t>
   </si>
   <si>
     <t>FD-14</t>
   </si>
   <si>
-    <t>上报</t>
-  </si>
-  <si>
-    <t>获取权限</t>
-  </si>
-  <si>
-    <t>头像权限、定位权限、相机权限，未授权不可使用</t>
+    <t>填报</t>
+  </si>
+  <si>
+    <t>根据类型填报信息，根据填报‘整改责任人’的手机号，自动推送到整改责任人</t>
   </si>
   <si>
     <t>FD-15</t>
   </si>
   <si>
-    <t>填报</t>
-  </si>
-  <si>
-    <t>根据类型填报信息，根据填报‘整改责任人’的手机号，自动推送到整改责任人</t>
+    <t>整改排查在线电子签名</t>
   </si>
   <si>
     <t>FD-16</t>
@@ -204,6 +204,15 @@
   </si>
   <si>
     <t>FD-17</t>
+  </si>
+  <si>
+    <t>修改密码</t>
+  </si>
+  <si>
+    <t>实现用户自定义修改登录密码，修改后返回登录页面</t>
+  </si>
+  <si>
+    <t>FD-18</t>
   </si>
   <si>
     <t>退出登录</t>
@@ -927,7 +936,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -941,9 +950,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -976,11 +982,23 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1518,7 +1536,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="B2:F24"/>
+  <dimension ref="B2:F25"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="2.69230769230769" customWidth="1"/>
@@ -1532,302 +1550,316 @@
       <c r="B2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="5"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="4"/>
     </row>
     <row r="3" ht="18" spans="2:6">
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="6" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="4" ht="36" spans="2:6">
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="D4" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="11"/>
-      <c r="F4" s="12" t="s">
+      <c r="E4" s="10"/>
+      <c r="F4" s="11" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="5" ht="36" spans="2:6">
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="13"/>
-      <c r="D5" s="10" t="s">
+      <c r="C5" s="12"/>
+      <c r="D5" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="11"/>
-      <c r="F5" s="12" t="s">
+      <c r="E5" s="10"/>
+      <c r="F5" s="11" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="6" ht="36" spans="2:6">
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="13"/>
-      <c r="D6" s="10" t="s">
+      <c r="C6" s="12"/>
+      <c r="D6" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="11"/>
-      <c r="F6" s="12" t="s">
+      <c r="E6" s="10"/>
+      <c r="F6" s="11" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="7" ht="36" spans="2:6">
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="13"/>
-      <c r="D7" s="9" t="s">
+      <c r="C7" s="12"/>
+      <c r="D7" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="E7" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="F7" s="12" t="s">
+      <c r="F7" s="11" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="8" ht="36" spans="2:6">
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="13"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="8" t="s">
+      <c r="C8" s="12"/>
+      <c r="D8" s="13"/>
+      <c r="E8" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="F8" s="12" t="s">
+      <c r="F8" s="11" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="9" ht="18" spans="2:6">
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="C9" s="13"/>
-      <c r="D9" s="9" t="s">
+      <c r="C9" s="12"/>
+      <c r="D9" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="E9" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="F9" s="12" t="s">
+      <c r="F9" s="11" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="10" ht="18" spans="2:6">
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="C10" s="13"/>
-      <c r="D10" s="13"/>
-      <c r="E10" s="8" t="s">
+      <c r="C10" s="12"/>
+      <c r="D10" s="12"/>
+      <c r="E10" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="F10" s="12" t="s">
+      <c r="F10" s="11" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="11" ht="17.6" spans="2:6">
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="C11" s="13"/>
-      <c r="D11" s="13"/>
-      <c r="E11" s="8" t="s">
+      <c r="C11" s="12"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="F11" s="15" t="s">
+      <c r="F11" s="14" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="12" ht="17.6" spans="2:6">
-      <c r="B12" s="8" t="s">
+      <c r="B12" s="7" t="s">
         <v>33</v>
       </c>
       <c r="C12" s="13"/>
       <c r="D12" s="13"/>
-      <c r="E12" s="8" t="s">
+      <c r="E12" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="F12" s="16"/>
-    </row>
-    <row r="13" ht="17.6" spans="2:6">
-      <c r="B13" s="8" t="s">
+      <c r="F12" s="15"/>
+    </row>
+    <row r="13" ht="36" spans="2:6">
+      <c r="B13" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="8" t="s">
+      <c r="C13" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="F13" s="17"/>
+      <c r="D13" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E13" s="10"/>
+      <c r="F13" s="11" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="14" ht="36" spans="2:6">
-      <c r="B14" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="C14" s="9" t="s">
+      <c r="B14" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="D14" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="E14" s="11"/>
-      <c r="F14" s="12" t="s">
+      <c r="C14" s="12"/>
+      <c r="D14" s="8" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="15" ht="36" spans="2:6">
-      <c r="B15" s="8" t="s">
+      <c r="E14" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="C15" s="13"/>
-      <c r="D15" s="9" t="s">
+      <c r="F14" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="E15" s="8" t="s">
+    </row>
+    <row r="15" ht="18" spans="2:6">
+      <c r="B15" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="F15" s="12" t="s">
+      <c r="C15" s="12"/>
+      <c r="D15" s="13"/>
+      <c r="E15" s="7" t="s">
         <v>43</v>
       </c>
+      <c r="F15" s="11" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="16" ht="18" spans="2:6">
-      <c r="B16" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="C16" s="13"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="8" t="s">
+      <c r="B16" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="F16" s="12" t="s">
+      <c r="C16" s="12"/>
+      <c r="D16" s="16" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="17" ht="18" spans="2:6">
-      <c r="B17" s="8" t="s">
+      <c r="E16" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="C17" s="13"/>
-      <c r="D17" s="9" t="s">
+      <c r="F16" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="E17" s="8" t="s">
+    </row>
+    <row r="17" ht="36" spans="2:6">
+      <c r="B17" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="F17" s="12" t="s">
+      <c r="C17" s="12"/>
+      <c r="D17" s="17"/>
+      <c r="E17" s="16" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="18" ht="36" spans="2:6">
-      <c r="B18" s="8" t="s">
+      <c r="F17" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="C18" s="13"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="8" t="s">
+    </row>
+    <row r="18" ht="18" spans="2:6">
+      <c r="B18" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="F18" s="12" t="s">
+      <c r="C18" s="12"/>
+      <c r="D18" s="17"/>
+      <c r="E18" s="18"/>
+      <c r="F18" s="11" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="19" ht="36" spans="2:6">
-      <c r="B19" s="8" t="s">
+      <c r="B19" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="C19" s="13"/>
-      <c r="D19" s="9" t="s">
+      <c r="C19" s="12"/>
+      <c r="D19" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="E19" s="8" t="s">
+      <c r="E19" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="F19" s="12" t="s">
+      <c r="F19" s="11" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="20" ht="18" spans="2:6">
-      <c r="B20" s="8" t="s">
+      <c r="B20" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="8" t="s">
+      <c r="C20" s="19"/>
+      <c r="D20" s="20"/>
+      <c r="E20" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="F20" s="12" t="s">
+      <c r="F20" s="11" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="21" ht="17.6" spans="2:6">
-      <c r="B21" s="18"/>
-      <c r="C21" s="18"/>
-      <c r="D21" s="18"/>
-      <c r="E21" s="18"/>
-      <c r="F21" s="19"/>
+    <row r="21" ht="18" spans="2:6">
+      <c r="B21" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C21" s="13"/>
+      <c r="D21" s="13"/>
+      <c r="E21" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="F21" s="11" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="22" ht="17.6" spans="2:6">
-      <c r="B22" s="18"/>
-      <c r="C22" s="18"/>
-      <c r="D22" s="18"/>
-      <c r="E22" s="18"/>
-      <c r="F22" s="19"/>
+      <c r="B22" s="21"/>
+      <c r="C22" s="21"/>
+      <c r="D22" s="21"/>
+      <c r="E22" s="21"/>
+      <c r="F22" s="22"/>
     </row>
     <row r="23" ht="17.6" spans="2:6">
-      <c r="B23" s="18"/>
-      <c r="C23" s="18"/>
-      <c r="D23" s="18"/>
-      <c r="E23" s="18"/>
-      <c r="F23" s="19"/>
+      <c r="B23" s="21"/>
+      <c r="C23" s="21"/>
+      <c r="D23" s="21"/>
+      <c r="E23" s="21"/>
+      <c r="F23" s="22"/>
     </row>
     <row r="24" ht="17.6" spans="2:6">
-      <c r="B24" s="18"/>
-      <c r="C24" s="18"/>
-      <c r="D24" s="18"/>
-      <c r="E24" s="18"/>
-      <c r="F24" s="19"/>
+      <c r="B24" s="21"/>
+      <c r="C24" s="21"/>
+      <c r="D24" s="21"/>
+      <c r="E24" s="21"/>
+      <c r="F24" s="22"/>
+    </row>
+    <row r="25" ht="17.6" spans="2:6">
+      <c r="B25" s="21"/>
+      <c r="C25" s="21"/>
+      <c r="D25" s="21"/>
+      <c r="E25" s="21"/>
+      <c r="F25" s="22"/>
     </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="14">
     <mergeCell ref="B2:F2"/>
     <mergeCell ref="D4:E4"/>
     <mergeCell ref="D5:E5"/>
     <mergeCell ref="D6:E6"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="C4:C13"/>
-    <mergeCell ref="C14:C20"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="C4:C12"/>
+    <mergeCell ref="C13:C21"/>
     <mergeCell ref="D7:D8"/>
-    <mergeCell ref="D9:D13"/>
-    <mergeCell ref="D15:D16"/>
-    <mergeCell ref="D17:D18"/>
-    <mergeCell ref="D19:D20"/>
-    <mergeCell ref="F11:F13"/>
+    <mergeCell ref="D9:D12"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="D16:D18"/>
+    <mergeCell ref="D19:D21"/>
+    <mergeCell ref="E17:E18"/>
+    <mergeCell ref="F11:F12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/demo/聊城经开区“高标准农田建设专项整改排查”项目功能清单.xlsx
+++ b/demo/聊城经开区“高标准农田建设专项整改排查”项目功能清单.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="66">
   <si>
     <t>聊城经开区“高标准农田建设专项整改排查”项目功能清单</t>
   </si>
@@ -86,19 +86,25 @@
     <t>街道台账</t>
   </si>
   <si>
-    <t>自动汇总各街道、村社区整改台账，支持按街道、起止日期筛选台账、导出台账表格</t>
+    <t>自动汇总各街道、村社区、自然村整改台账，支持按街道、起止日期筛选台账、导出台账表格</t>
   </si>
   <si>
     <t>FD-05</t>
   </si>
   <si>
+    <t>实现'移交数量'栏的在线编辑于保存，提交后记录造作日志</t>
+  </si>
+  <si>
+    <t>FD-06</t>
+  </si>
+  <si>
     <t>街道排查汇总</t>
   </si>
   <si>
     <t>自动汇总各街道整改台账，支持按街道、起止日期筛选台账、导出台账表格</t>
   </si>
   <si>
-    <t>FD-06</t>
+    <t>FD-07</t>
   </si>
   <si>
     <t>系统配置</t>
@@ -110,16 +116,16 @@
     <t>实现管委会/街道/村社区三级组织架构维护</t>
   </si>
   <si>
-    <t>FD-07</t>
+    <t>FD-08</t>
   </si>
   <si>
     <t>工作人员</t>
   </si>
   <si>
-    <t>实现平台工作人员的账号权限开设</t>
-  </si>
-  <si>
-    <t>FD-08</t>
+    <t>实现平台工作人员的账号权限开设、重置密码</t>
+  </si>
+  <si>
+    <t>FD-09</t>
   </si>
   <si>
     <t>角色权限</t>
@@ -128,13 +134,13 @@
     <t>提供对系统内静态参数、角色权限进行管理的功能</t>
   </si>
   <si>
-    <t>FD-09</t>
+    <t>FD-10</t>
   </si>
   <si>
     <t>操作日志</t>
   </si>
   <si>
-    <t>FD-10</t>
+    <t>FD-11</t>
   </si>
   <si>
     <t>小程序</t>
@@ -143,7 +149,7 @@
     <t>实现账号密码+验证码登录，登录后根据所属权限加载相应数据</t>
   </si>
   <si>
-    <t>FD-11</t>
+    <t>FD-12</t>
   </si>
   <si>
     <t>待办</t>
@@ -155,7 +161,7 @@
     <t>展示当前账号待整改的待办列表，支持点击定位查看地理位置</t>
   </si>
   <si>
-    <t>FD-12</t>
+    <t>FD-13</t>
   </si>
   <si>
     <t>详情</t>
@@ -164,7 +170,7 @@
     <t>查看待整改详细信息，填报整改反馈后闭环处置</t>
   </si>
   <si>
-    <t>FD-13</t>
+    <t>FD-14</t>
   </si>
   <si>
     <t>上报</t>
@@ -176,7 +182,7 @@
     <t>头像权限、定位权限、相机权限，未授权不可使用</t>
   </si>
   <si>
-    <t>FD-14</t>
+    <t>FD-15</t>
   </si>
   <si>
     <t>填报</t>
@@ -185,13 +191,13 @@
     <t>根据类型填报信息，根据填报‘整改责任人’的手机号，自动推送到整改责任人</t>
   </si>
   <si>
-    <t>FD-15</t>
+    <t>FD-16</t>
   </si>
   <si>
     <t>整改排查在线电子签名</t>
   </si>
   <si>
-    <t>FD-16</t>
+    <t>FD-17</t>
   </si>
   <si>
     <t>我的</t>
@@ -203,7 +209,7 @@
     <t>个人信息展示与统计，可查看与当前账号相关的上报、待整改、已整改的列表及详情、处置</t>
   </si>
   <si>
-    <t>FD-17</t>
+    <t>FD-18</t>
   </si>
   <si>
     <t>修改密码</t>
@@ -212,7 +218,7 @@
     <t>实现用户自定义修改登录密码，修改后返回登录页面</t>
   </si>
   <si>
-    <t>FD-18</t>
+    <t>FD-19</t>
   </si>
   <si>
     <t>退出登录</t>
@@ -936,7 +942,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -976,29 +982,23 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1536,7 +1536,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="B2:F25"/>
+  <dimension ref="B2:F26"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="2.69230769230769" customWidth="1"/>
@@ -1621,7 +1621,7 @@
       <c r="D7" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="E7" s="13" t="s">
         <v>18</v>
       </c>
       <c r="F7" s="11" t="s">
@@ -1633,233 +1633,245 @@
         <v>20</v>
       </c>
       <c r="C8" s="12"/>
-      <c r="D8" s="13"/>
-      <c r="E8" s="7" t="s">
+      <c r="D8" s="14"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="F8" s="11" t="s">
+    </row>
+    <row r="9" ht="36" spans="2:6">
+      <c r="B9" s="7" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="9" ht="18" spans="2:6">
-      <c r="B9" s="7" t="s">
+      <c r="C9" s="12"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="C9" s="12"/>
-      <c r="D9" s="8" t="s">
+      <c r="F9" s="11" t="s">
         <v>24</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F9" s="11" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="10" ht="18" spans="2:6">
       <c r="B10" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" s="12"/>
+      <c r="D10" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="E10" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="7" t="s">
+      <c r="F10" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="F10" s="11" t="s">
+    </row>
+    <row r="11" ht="18" spans="2:6">
+      <c r="B11" s="7" t="s">
         <v>29</v>
-      </c>
-    </row>
-    <row r="11" ht="17.6" spans="2:6">
-      <c r="B11" s="7" t="s">
-        <v>30</v>
       </c>
       <c r="C11" s="12"/>
       <c r="D11" s="12"/>
       <c r="E11" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="F11" s="11" t="s">
         <v>31</v>
-      </c>
-      <c r="F11" s="14" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="12" ht="17.6" spans="2:6">
       <c r="B12" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" s="12"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="C12" s="13"/>
-      <c r="D12" s="13"/>
-      <c r="E12" s="7" t="s">
+      <c r="F12" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="F12" s="15"/>
-    </row>
-    <row r="13" ht="36" spans="2:6">
+    </row>
+    <row r="13" ht="17.6" spans="2:6">
       <c r="B13" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="C13" s="16"/>
+      <c r="D13" s="16"/>
+      <c r="E13" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="D13" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="E13" s="10"/>
-      <c r="F13" s="11" t="s">
-        <v>37</v>
-      </c>
+      <c r="F13" s="18"/>
     </row>
     <row r="14" ht="36" spans="2:6">
       <c r="B14" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C14" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="C14" s="12"/>
-      <c r="D14" s="8" t="s">
+      <c r="D14" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="10"/>
+      <c r="F14" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="E14" s="7" t="s">
+    </row>
+    <row r="15" ht="36" spans="2:6">
+      <c r="B15" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="F14" s="11" t="s">
+      <c r="C15" s="12"/>
+      <c r="D15" s="8" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="15" ht="18" spans="2:6">
-      <c r="B15" s="7" t="s">
+      <c r="E15" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="C15" s="12"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="7" t="s">
+      <c r="F15" s="11" t="s">
         <v>43</v>
-      </c>
-      <c r="F15" s="11" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="16" ht="18" spans="2:6">
       <c r="B16" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C16" s="12"/>
+      <c r="D16" s="16"/>
+      <c r="E16" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="C16" s="12"/>
-      <c r="D16" s="16" t="s">
+      <c r="F16" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="E16" s="7" t="s">
+    </row>
+    <row r="17" ht="18" spans="2:6">
+      <c r="B17" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="F16" s="11" t="s">
+      <c r="C17" s="12"/>
+      <c r="D17" s="8" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="17" ht="36" spans="2:6">
-      <c r="B17" s="7" t="s">
+      <c r="E17" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="C17" s="12"/>
-      <c r="D17" s="17"/>
-      <c r="E17" s="16" t="s">
+      <c r="F17" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="F17" s="11" t="s">
+    </row>
+    <row r="18" ht="36" spans="2:6">
+      <c r="B18" s="7" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="18" ht="18" spans="2:6">
-      <c r="B18" s="7" t="s">
+      <c r="C18" s="12"/>
+      <c r="D18" s="12"/>
+      <c r="E18" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="C18" s="12"/>
-      <c r="D18" s="17"/>
-      <c r="E18" s="18"/>
       <c r="F18" s="11" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="19" ht="36" spans="2:6">
+    <row r="19" ht="18" spans="2:6">
       <c r="B19" s="7" t="s">
         <v>54</v>
       </c>
       <c r="C19" s="12"/>
-      <c r="D19" s="8" t="s">
+      <c r="D19" s="12"/>
+      <c r="E19" s="16"/>
+      <c r="F19" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="E19" s="7" t="s">
+    </row>
+    <row r="20" ht="36" spans="2:6">
+      <c r="B20" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="F19" s="11" t="s">
+      <c r="C20" s="12"/>
+      <c r="D20" s="8" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="20" ht="18" spans="2:6">
-      <c r="B20" s="7" t="s">
+      <c r="E20" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="C20" s="19"/>
-      <c r="D20" s="20"/>
-      <c r="E20" s="7" t="s">
+      <c r="F20" s="11" t="s">
         <v>59</v>
-      </c>
-      <c r="F20" s="11" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="21" ht="18" spans="2:6">
       <c r="B21" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="C21" s="12"/>
+      <c r="D21" s="12"/>
+      <c r="E21" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="C21" s="13"/>
-      <c r="D21" s="13"/>
-      <c r="E21" s="7" t="s">
+      <c r="F21" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="F21" s="11" t="s">
+    </row>
+    <row r="22" ht="18" spans="2:6">
+      <c r="B22" s="7" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="22" ht="17.6" spans="2:6">
-      <c r="B22" s="21"/>
-      <c r="C22" s="21"/>
-      <c r="D22" s="21"/>
-      <c r="E22" s="21"/>
-      <c r="F22" s="22"/>
+      <c r="C22" s="16"/>
+      <c r="D22" s="16"/>
+      <c r="E22" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="F22" s="11" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="23" ht="17.6" spans="2:6">
-      <c r="B23" s="21"/>
-      <c r="C23" s="21"/>
-      <c r="D23" s="21"/>
-      <c r="E23" s="21"/>
-      <c r="F23" s="22"/>
+      <c r="B23" s="19"/>
+      <c r="C23" s="19"/>
+      <c r="D23" s="19"/>
+      <c r="E23" s="19"/>
+      <c r="F23" s="20"/>
     </row>
     <row r="24" ht="17.6" spans="2:6">
-      <c r="B24" s="21"/>
-      <c r="C24" s="21"/>
-      <c r="D24" s="21"/>
-      <c r="E24" s="21"/>
-      <c r="F24" s="22"/>
+      <c r="B24" s="19"/>
+      <c r="C24" s="19"/>
+      <c r="D24" s="19"/>
+      <c r="E24" s="19"/>
+      <c r="F24" s="20"/>
     </row>
     <row r="25" ht="17.6" spans="2:6">
-      <c r="B25" s="21"/>
-      <c r="C25" s="21"/>
-      <c r="D25" s="21"/>
-      <c r="E25" s="21"/>
-      <c r="F25" s="22"/>
+      <c r="B25" s="19"/>
+      <c r="C25" s="19"/>
+      <c r="D25" s="19"/>
+      <c r="E25" s="19"/>
+      <c r="F25" s="20"/>
+    </row>
+    <row r="26" ht="17.6" spans="2:6">
+      <c r="B26" s="19"/>
+      <c r="C26" s="19"/>
+      <c r="D26" s="19"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="20"/>
     </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="15">
     <mergeCell ref="B2:F2"/>
     <mergeCell ref="D4:E4"/>
     <mergeCell ref="D5:E5"/>
     <mergeCell ref="D6:E6"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="C4:C12"/>
-    <mergeCell ref="C13:C21"/>
-    <mergeCell ref="D7:D8"/>
-    <mergeCell ref="D9:D12"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="D16:D18"/>
-    <mergeCell ref="D19:D21"/>
-    <mergeCell ref="E17:E18"/>
-    <mergeCell ref="F11:F12"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="C4:C13"/>
+    <mergeCell ref="C14:C22"/>
+    <mergeCell ref="D7:D9"/>
+    <mergeCell ref="D10:D13"/>
+    <mergeCell ref="D15:D16"/>
+    <mergeCell ref="D17:D19"/>
+    <mergeCell ref="D20:D22"/>
+    <mergeCell ref="E7:E8"/>
+    <mergeCell ref="E18:E19"/>
+    <mergeCell ref="F12:F13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
